--- a/TeamCalcs_SheetExport.xlsx
+++ b/TeamCalcs_SheetExport.xlsx
@@ -456,84 +456,84 @@
     <row r="9">
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>112184.255</t>
+          <t>76786.492</t>
         </is>
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>105101.699</t>
+          <t>70413.337</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>117962.780</t>
+          <t>83474.925</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>error margin: +/-0.48%</t>
+          <t>error margin: +/-0.74%</t>
         </is>
       </c>
       <c r="R9" s="1" t="inlineStr">
         <is>
-          <t>124927.721</t>
+          <t>83555.088</t>
         </is>
       </c>
       <c r="T9" s="1" t="inlineStr">
         <is>
-          <t>115745.095</t>
+          <t>79196.481</t>
         </is>
       </c>
       <c r="V9" s="1" t="inlineStr">
         <is>
-          <t>130262.723</t>
+          <t>87216.702</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>error margin: +/-0.50%</t>
+          <t>error margin: +/-0.43%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>- ELABANGER  avg DMG: 30726958.215  (64.0% of Evanescia's DMG)</t>
+          <t>- ELAPUNCH  avg DMG: 17468895.875  (59.8% of Sparxie's DMG)</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>- ELAPUNCH  avg DMG: 3245783.425  (66.5% of ElationMC's DMG)</t>
+          <t>- ELAPUNCH  avg DMG: 3349822.915  (64.0% of ElationMC's DMG)</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>- ELAPUNCH  avg DMG: 6078500.295  (73.4% of YaoGuang's DMG)</t>
+          <t>- ELAPUNCH  avg DMG: 5743271.415  (75.7% of YaoGuang's DMG)</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>- ELABANGER  avg DMG: 107184.545  (64.1% of Pearl's DMG)</t>
+          <t>- ELABANGER  avg DMG: 68301.665  (57.5% of Pearl's DMG)</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>- ELABANGER  avg DMG: 34751457.909  (64.6% of Evanescia's DMG)</t>
+          <t>- ELAPUNCH  avg DMG: 18728986.878  (58.7% of Sparxie's DMG)</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>- ELAPUNCH  avg DMG: 3501443.185  (66.6% of ElationMC's DMG)</t>
+          <t>- ELAPUNCH  avg DMG: 3624443.779  (64.1% of ElationMC's DMG)</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t>- ELAPUNCH  avg DMG: 6558126.195  (72.4% of YaoGuang's DMG)</t>
+          <t>- ELAPUNCH  avg DMG: 6198123.241  (75.7% of YaoGuang's DMG)</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>- ELABANGER  avg DMG: 122841.786  (56.6% of Pearl's DMG)</t>
+          <t>- BSC  avg DMG: 80566.455  (50.2% of Pearl's DMG)</t>
         </is>
       </c>
     </row>
@@ -541,42 +541,42 @@
     <row r="14">
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>- ELAPUNCH  avg DMG: 13777758.862  (28.7% of Evanescia's DMG)</t>
+          <t>- ELABANGER  avg DMG: 10701882.514  (36.6% of Sparxie's DMG)</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>- ELABANGER  avg DMG: 1517309.852  (31.1% of ElationMC's DMG)</t>
+          <t>- ELABANGER  avg DMG: 1773795.778  (33.9% of ElationMC's DMG)</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>- ELABANGER  avg DMG: 2101946.974  (25.4% of YaoGuang's DMG)</t>
+          <t>- ELABANGER  avg DMG: 1819001.637  (24.0% of YaoGuang's DMG)</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>- BSC  avg DMG: 60052.310  (35.9% of Pearl's DMG)</t>
+          <t>- BSC  avg DMG: 50435.214  (42.5% of Pearl's DMG)</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>- ELAPUNCH  avg DMG: 14817706.028  (27.5% of Evanescia's DMG)</t>
+          <t>- ELABANGER  avg DMG: 11874300.871  (37.2% of Sparxie's DMG)</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>- ELABANGER  avg DMG: 1620133.121  (30.8% of ElationMC's DMG)</t>
+          <t>- ELABANGER  avg DMG: 1895713.976  (33.5% of ElationMC's DMG)</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t>- ELABANGER  avg DMG: 2368527.607  (26.2% of YaoGuang's DMG)</t>
+          <t>- ELABANGER  avg DMG: 1955394.644  (23.9% of YaoGuang's DMG)</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>- BSC  avg DMG: 94257.009  (43.4% of Pearl's DMG)</t>
+          <t>- ELABANGER  avg DMG: 80074.767  (49.8% of Pearl's DMG)</t>
         </is>
       </c>
     </row>
@@ -584,17 +584,17 @@
     <row r="16">
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>- ULT  avg DMG: 1908102.496  (4.0% of Evanescia's DMG)</t>
+          <t>- BSC  avg DMG: 598775.127  (2.0% of Sparxie's DMG)</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>- SKL  avg DMG: 117271.892  (2.4% of ElationMC's DMG)</t>
+          <t>- SKL  avg DMG: 111690.232  (2.1% of ElationMC's DMG)</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>- BRK  avg DMG: 66965.746  (0.8% of YaoGuang's DMG)</t>
+          <t>- BSC  avg DMG: 26505.789  (0.3% of YaoGuang's DMG)</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -604,17 +604,17 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>- ULT  avg DMG: 2305622.703  (4.3% of Evanescia's DMG)</t>
+          <t>- BSC  avg DMG: 732907.267  (2.3% of Sparxie's DMG)</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>- SKL  avg DMG: 133642.308  (2.5% of ElationMC's DMG)</t>
+          <t>- SKL  avg DMG: 130362.433  (2.3% of ElationMC's DMG)</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>- BRK  avg DMG: 89162.625  (1.0% of YaoGuang's DMG)</t>
+          <t>- BSC  avg DMG: 30558.393  (0.4% of YaoGuang's DMG)</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
@@ -627,54 +627,54 @@
     <row r="18">
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Evanescia</t>
+          <t>Sparxie</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>87330.399</t>
+          <t>53149.838</t>
         </is>
       </c>
       <c r="X18" s="4" t="inlineStr">
         <is>
-          <t>Evanescia</t>
+          <t>Sparxie</t>
         </is>
       </c>
       <c r="Y18" s="4" t="inlineStr">
         <is>
-          <t>97823.474</t>
+          <t>57986.129</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>4328429.3</t>
+          <t>8675940.8</t>
         </is>
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>760333.5</t>
+          <t>6792929.7</t>
         </is>
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
-          <t>2036510.8</t>
+          <t>306704.0</t>
         </is>
       </c>
       <c r="J19" s="1" t="inlineStr">
         <is>
-          <t>28012.0</t>
+          <t>5881.5</t>
         </is>
       </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>754173.2</t>
+          <t>1279383.4</t>
         </is>
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
-          <t>749399.8</t>
+          <t>291042.2</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -684,37 +684,37 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>8873.391</t>
+          <t>9518.744</t>
         </is>
       </c>
       <c r="R19" s="1" t="inlineStr">
         <is>
-          <t>4773518.3</t>
+          <t>10276560.2</t>
         </is>
       </c>
       <c r="S19" s="1" t="inlineStr">
         <is>
-          <t>805119.3</t>
+          <t>8248884.1</t>
         </is>
       </c>
       <c r="T19" s="1" t="inlineStr">
         <is>
-          <t>2100906.3</t>
+          <t>287312.9</t>
         </is>
       </c>
       <c r="U19" s="1" t="inlineStr">
         <is>
-          <t>82697.7</t>
+          <t>22062.2</t>
         </is>
       </c>
       <c r="V19" s="1" t="inlineStr">
         <is>
-          <t>891957.3</t>
+          <t>1287393.3</t>
         </is>
       </c>
       <c r="W19" s="1" t="inlineStr">
         <is>
-          <t>892837.8</t>
+          <t>430907.7</t>
         </is>
       </c>
       <c r="X19" s="4" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="Y19" s="4" t="inlineStr">
         <is>
-          <t>9554.943</t>
+          <t>10273.673</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>15054.120</t>
+          <t>13797.780</t>
         </is>
       </c>
       <c r="X20" s="4" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="Y20" s="4" t="inlineStr">
         <is>
-          <t>16459.682</t>
+          <t>14880.139</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>304.067</t>
+          <t>215.885</t>
         </is>
       </c>
       <c r="X21" s="4" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="Y21" s="4" t="inlineStr">
         <is>
-          <t>394.725</t>
+          <t>292.075</t>
         </is>
       </c>
     </row>

--- a/TeamCalcs_SheetExport.xlsx
+++ b/TeamCalcs_SheetExport.xlsx
@@ -450,90 +450,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="G9:Y21"/>
+  <dimension ref="G9:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="9">
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>76786.492</t>
+          <t>86613.032</t>
         </is>
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>70413.337</t>
+          <t>76420.889</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>83474.925</t>
+          <t>100127.491</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>error margin: +/-0.74%</t>
-        </is>
-      </c>
-      <c r="R9" s="1" t="inlineStr">
-        <is>
-          <t>83555.088</t>
-        </is>
-      </c>
-      <c r="T9" s="1" t="inlineStr">
-        <is>
-          <t>79196.481</t>
-        </is>
-      </c>
-      <c r="V9" s="1" t="inlineStr">
-        <is>
-          <t>87216.702</t>
-        </is>
-      </c>
-      <c r="X9" s="2" t="inlineStr">
-        <is>
-          <t>error margin: +/-0.43%</t>
+          <t>error margin: +/-1.07%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>- ELAPUNCH  avg DMG: 17468895.875  (59.8% of Sparxie's DMG)</t>
+          <t>- ELABANGER  avg DMG: 29390484.863  (86.5% of SilverWolf999's DMG)</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>- ELAPUNCH  avg DMG: 3349822.915  (64.0% of ElationMC's DMG)</t>
+          <t>- ELAPUNCH  avg DMG: 5601962.174  (63.2% of Sparxie's DMG)</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>- ELAPUNCH  avg DMG: 5743271.415  (75.7% of YaoGuang's DMG)</t>
+          <t>- ELAPUNCH  avg DMG: 3359353.570  (71.2% of YaoGuang's DMG)</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>- ELABANGER  avg DMG: 68301.665  (57.5% of Pearl's DMG)</t>
-        </is>
-      </c>
-      <c r="R12" s="3" t="inlineStr">
-        <is>
-          <t>- ELAPUNCH  avg DMG: 18728986.878  (58.7% of Sparxie's DMG)</t>
-        </is>
-      </c>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t>- ELAPUNCH  avg DMG: 3624443.779  (64.1% of ElationMC's DMG)</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t>- ELAPUNCH  avg DMG: 6198123.241  (75.7% of YaoGuang's DMG)</t>
-        </is>
-      </c>
-      <c r="X12" s="3" t="inlineStr">
-        <is>
-          <t>- BSC  avg DMG: 80566.455  (50.2% of Pearl's DMG)</t>
+          <t>- ELABANGER  avg DMG: 48980.375  (61.5% of Pearl's DMG)</t>
         </is>
       </c>
     </row>
@@ -541,42 +501,22 @@
     <row r="14">
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>- ELABANGER  avg DMG: 10701882.514  (36.6% of Sparxie's DMG)</t>
+          <t>- ELAPUNCH  avg DMG: 4448586.842  (13.1% of SilverWolf999's DMG)</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>- ELABANGER  avg DMG: 1773795.778  (33.9% of ElationMC's DMG)</t>
+          <t>- ELABANGER  avg DMG: 2953835.107  (33.3% of Sparxie's DMG)</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>- ELABANGER  avg DMG: 1819001.637  (24.0% of YaoGuang's DMG)</t>
+          <t>- ELABANGER  avg DMG: 1329900.849  (28.2% of YaoGuang's DMG)</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>- BSC  avg DMG: 50435.214  (42.5% of Pearl's DMG)</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t>- ELABANGER  avg DMG: 11874300.871  (37.2% of Sparxie's DMG)</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t>- ELABANGER  avg DMG: 1895713.976  (33.5% of ElationMC's DMG)</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t>- ELABANGER  avg DMG: 1955394.644  (23.9% of YaoGuang's DMG)</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t>- ELABANGER  avg DMG: 80074.767  (49.8% of Pearl's DMG)</t>
+          <t>- BSC  avg DMG: 30663.013  (38.5% of Pearl's DMG)</t>
         </is>
       </c>
     </row>
@@ -584,40 +524,20 @@
     <row r="16">
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>- BSC  avg DMG: 598775.127  (2.0% of Sparxie's DMG)</t>
+          <t>- SKL  avg DMG: 93999.533  (0.3% of SilverWolf999's DMG)</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>- SKL  avg DMG: 111690.232  (2.1% of ElationMC's DMG)</t>
+          <t>- BSC  avg DMG: 250361.503  (2.8% of Sparxie's DMG)</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>- BSC  avg DMG: 26505.789  (0.3% of YaoGuang's DMG)</t>
+          <t>- BSC  avg DMG: 26310.959  (0.6% of YaoGuang's DMG)</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>- SKL  avg DMG: 0.000  (0.0% of Pearl's DMG)</t>
-        </is>
-      </c>
-      <c r="R16" s="3" t="inlineStr">
-        <is>
-          <t>- BSC  avg DMG: 732907.267  (2.3% of Sparxie's DMG)</t>
-        </is>
-      </c>
-      <c r="T16" s="3" t="inlineStr">
-        <is>
-          <t>- SKL  avg DMG: 130362.433  (2.3% of ElationMC's DMG)</t>
-        </is>
-      </c>
-      <c r="V16" s="3" t="inlineStr">
-        <is>
-          <t>- BSC  avg DMG: 30558.393  (0.4% of YaoGuang's DMG)</t>
-        </is>
-      </c>
-      <c r="X16" s="3" t="inlineStr">
         <is>
           <t>- SKL  avg DMG: 0.000  (0.0% of Pearl's DMG)</t>
         </is>
@@ -627,104 +547,54 @@
     <row r="18">
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Sparxie</t>
+          <t>SilverWolf999</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>53149.838</t>
-        </is>
-      </c>
-      <c r="X18" s="4" t="inlineStr">
-        <is>
-          <t>Sparxie</t>
-        </is>
-      </c>
-      <c r="Y18" s="4" t="inlineStr">
-        <is>
-          <t>57986.129</t>
+          <t>61786.112</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>8675940.8</t>
+          <t>847561.8</t>
         </is>
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>6792929.7</t>
+          <t>556397.3</t>
         </is>
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
-          <t>306704.0</t>
+          <t>93554.9</t>
         </is>
       </c>
       <c r="J19" s="1" t="inlineStr">
         <is>
-          <t>5881.5</t>
+          <t>197609.7</t>
         </is>
       </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>1279383.4</t>
+          <t>/</t>
         </is>
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
-          <t>291042.2</t>
+          <t>/</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>ElationMC</t>
+          <t>Sparxie</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>9518.744</t>
-        </is>
-      </c>
-      <c r="R19" s="1" t="inlineStr">
-        <is>
-          <t>10276560.2</t>
-        </is>
-      </c>
-      <c r="S19" s="1" t="inlineStr">
-        <is>
-          <t>8248884.1</t>
-        </is>
-      </c>
-      <c r="T19" s="1" t="inlineStr">
-        <is>
-          <t>287312.9</t>
-        </is>
-      </c>
-      <c r="U19" s="1" t="inlineStr">
-        <is>
-          <t>22062.2</t>
-        </is>
-      </c>
-      <c r="V19" s="1" t="inlineStr">
-        <is>
-          <t>1287393.3</t>
-        </is>
-      </c>
-      <c r="W19" s="1" t="inlineStr">
-        <is>
-          <t>430907.7</t>
-        </is>
-      </c>
-      <c r="X19" s="4" t="inlineStr">
-        <is>
-          <t>ElationMC</t>
-        </is>
-      </c>
-      <c r="Y19" s="4" t="inlineStr">
-        <is>
-          <t>10273.673</t>
+          <t>16108.359</t>
         </is>
       </c>
     </row>
@@ -736,17 +606,7 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>13797.780</t>
-        </is>
-      </c>
-      <c r="X20" s="4" t="inlineStr">
-        <is>
-          <t>YaoGuang</t>
-        </is>
-      </c>
-      <c r="Y20" s="4" t="inlineStr">
-        <is>
-          <t>14880.139</t>
+          <t>8573.755</t>
         </is>
       </c>
     </row>
@@ -758,63 +618,31 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>215.885</t>
-        </is>
-      </c>
-      <c r="X21" s="4" t="inlineStr">
-        <is>
-          <t>Pearl</t>
-        </is>
-      </c>
-      <c r="Y21" s="4" t="inlineStr">
-        <is>
-          <t>292.075</t>
+          <t>144.806</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="44">
-    <mergeCell ref="R19:R20"/>
+  <mergeCells count="22">
     <mergeCell ref="M16:N17"/>
-    <mergeCell ref="R12:S13"/>
-    <mergeCell ref="T12:U13"/>
     <mergeCell ref="I12:J13"/>
     <mergeCell ref="K12:L13"/>
     <mergeCell ref="M12:N13"/>
     <mergeCell ref="K9:L9"/>
     <mergeCell ref="M9:N9"/>
-    <mergeCell ref="V19:V20"/>
     <mergeCell ref="G14:H15"/>
     <mergeCell ref="G19:G20"/>
     <mergeCell ref="I14:J15"/>
     <mergeCell ref="K14:L15"/>
     <mergeCell ref="M14:N15"/>
-    <mergeCell ref="S19:S20"/>
-    <mergeCell ref="X14:Y15"/>
     <mergeCell ref="J19:J20"/>
-    <mergeCell ref="V16:W17"/>
-    <mergeCell ref="V12:W13"/>
     <mergeCell ref="G16:H17"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="T16:U17"/>
-    <mergeCell ref="V9:W9"/>
-    <mergeCell ref="R14:S15"/>
     <mergeCell ref="H19:H20"/>
-    <mergeCell ref="X9:Y9"/>
     <mergeCell ref="K16:L17"/>
     <mergeCell ref="G12:H13"/>
-    <mergeCell ref="X12:Y13"/>
-    <mergeCell ref="V14:W15"/>
     <mergeCell ref="I19:I20"/>
-    <mergeCell ref="T19:T20"/>
     <mergeCell ref="K19:K20"/>
-    <mergeCell ref="U19:U20"/>
-    <mergeCell ref="W19:W20"/>
-    <mergeCell ref="T14:U15"/>
-    <mergeCell ref="R16:S17"/>
-    <mergeCell ref="X16:Y17"/>
     <mergeCell ref="I16:J17"/>
-    <mergeCell ref="R9:S9"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="L19:L20"/>
